--- a/2024AIDataScienceGNRClub/Advanced Excel/feb1.xlsx
+++ b/2024AIDataScienceGNRClub/Advanced Excel/feb1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4ED60C-F49B-446A-9AEB-C36CF28761CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F04C87D-DF2D-4E3B-976D-90269FE977D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{0A4A095B-CF88-4750-B130-5412916BE60C}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="89">
   <si>
     <t>S. No</t>
   </si>
@@ -211,6 +211,90 @@
   </si>
   <si>
     <t>How many unique venues are there in IPL?</t>
+  </si>
+  <si>
+    <t>Newlands</t>
+  </si>
+  <si>
+    <t>St George's Park</t>
+  </si>
+  <si>
+    <t>Kingsmead</t>
+  </si>
+  <si>
+    <t>SuperSport Park</t>
+  </si>
+  <si>
+    <t>Buffalo Park</t>
+  </si>
+  <si>
+    <t>New Wanderers Stadium</t>
+  </si>
+  <si>
+    <t>De Beers Diamond Oval</t>
+  </si>
+  <si>
+    <t>OUTsurance Oval</t>
+  </si>
+  <si>
+    <t>Brabourne Stadium</t>
+  </si>
+  <si>
+    <t>Sardar Patel Stadium, Motera</t>
+  </si>
+  <si>
+    <t>Barabati Stadium</t>
+  </si>
+  <si>
+    <t>Vidarbha Cricket Association Stadium, Jamtha</t>
+  </si>
+  <si>
+    <t>Himachal Pradesh Cricket Association Stadium</t>
+  </si>
+  <si>
+    <t>Nehru Stadium</t>
+  </si>
+  <si>
+    <t>Holkar Cricket Stadium</t>
+  </si>
+  <si>
+    <t>Dr. Y.S. Rajasekhara Reddy ACA-VDCA Cricket Stadium</t>
+  </si>
+  <si>
+    <t>Subrata Roy Sahara Stadium</t>
+  </si>
+  <si>
+    <t>Shaheed Veer Narayan Singh International Stadium</t>
+  </si>
+  <si>
+    <t>JSCA International Stadium Complex</t>
+  </si>
+  <si>
+    <t>Sheikh Zayed Stadium</t>
+  </si>
+  <si>
+    <t>Sharjah Cricket Stadium</t>
+  </si>
+  <si>
+    <t>Dubai International Cricket Stadium</t>
+  </si>
+  <si>
+    <t>Maharashtra Cricket Association Stadium</t>
+  </si>
+  <si>
+    <t>Punjab Cricket Association IS Bindra Stadium, Mohali</t>
+  </si>
+  <si>
+    <t>Saurashtra Cricket Association Stadium</t>
+  </si>
+  <si>
+    <t>Green Park</t>
+  </si>
+  <si>
+    <t>M.Chinnaswamy Stadium</t>
+  </si>
+  <si>
+    <t>Unique Venues:</t>
   </si>
 </sst>
 </file>
@@ -308,6 +392,2555 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Charts!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales in Lacs</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Charts!$A$2:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2010</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Charts!$B$2:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6621-42D0-B329-5C7EDBA8A928}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="621091528"/>
+        <c:axId val="621094408"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="621091528"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="621094408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="621094408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="621091528"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:glow rad="101600">
+            <a:schemeClr val="accent2">
+              <a:satMod val="175000"/>
+              <a:alpha val="40000"/>
+            </a:schemeClr>
+          </a:glow>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT/>
+        </a:sp3d>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent1">
+        <a:lumMod val="20000"/>
+        <a:lumOff val="80000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="30"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Charts!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales in Lacs</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Charts!$B$2:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9B82-48D1-9FA9-39D353001870}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredPieSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Charts!$A$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Year</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:effectLst>
+                    <a:outerShdw blurRad="228600" dist="127000" dir="2700000" sx="91000" sy="91000" algn="tl" rotWithShape="0">
+                      <a:prstClr val="black">
+                        <a:alpha val="40000"/>
+                      </a:prstClr>
+                    </a:outerShdw>
+                  </a:effectLst>
+                  <a:scene3d>
+                    <a:camera prst="orthographicFront"/>
+                    <a:lightRig rig="threePt" dir="t"/>
+                  </a:scene3d>
+                  <a:sp3d prstMaterial="metal">
+                    <a:bevelT prst="relaxedInset"/>
+                    <a:contourClr>
+                      <a:srgbClr val="000000"/>
+                    </a:contourClr>
+                  </a:sp3d>
+                </c:spPr>
+                <c:dPt>
+                  <c:idx val="0"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="25400">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst>
+                      <a:outerShdw blurRad="228600" dist="127000" dir="2700000" sx="91000" sy="91000" algn="tl" rotWithShape="0">
+                        <a:prstClr val="black">
+                          <a:alpha val="40000"/>
+                        </a:prstClr>
+                      </a:outerShdw>
+                    </a:effectLst>
+                    <a:scene3d>
+                      <a:camera prst="orthographicFront"/>
+                      <a:lightRig rig="threePt" dir="t"/>
+                    </a:scene3d>
+                    <a:sp3d contourW="25400" prstMaterial="metal">
+                      <a:bevelT prst="relaxedInset"/>
+                      <a:contourClr>
+                        <a:schemeClr val="lt1"/>
+                      </a:contourClr>
+                    </a:sp3d>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="1"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="25400">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst>
+                      <a:outerShdw blurRad="228600" dist="127000" dir="2700000" sx="91000" sy="91000" algn="tl" rotWithShape="0">
+                        <a:prstClr val="black">
+                          <a:alpha val="40000"/>
+                        </a:prstClr>
+                      </a:outerShdw>
+                    </a:effectLst>
+                    <a:scene3d>
+                      <a:camera prst="orthographicFront"/>
+                      <a:lightRig rig="threePt" dir="t"/>
+                    </a:scene3d>
+                    <a:sp3d contourW="25400" prstMaterial="metal">
+                      <a:bevelT prst="relaxedInset"/>
+                      <a:contourClr>
+                        <a:schemeClr val="lt1"/>
+                      </a:contourClr>
+                    </a:sp3d>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="2"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="25400">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst>
+                      <a:outerShdw blurRad="228600" dist="127000" dir="2700000" sx="91000" sy="91000" algn="tl" rotWithShape="0">
+                        <a:prstClr val="black">
+                          <a:alpha val="40000"/>
+                        </a:prstClr>
+                      </a:outerShdw>
+                    </a:effectLst>
+                    <a:scene3d>
+                      <a:camera prst="orthographicFront"/>
+                      <a:lightRig rig="threePt" dir="t"/>
+                    </a:scene3d>
+                    <a:sp3d contourW="25400" prstMaterial="metal">
+                      <a:bevelT prst="relaxedInset"/>
+                      <a:contourClr>
+                        <a:schemeClr val="lt1"/>
+                      </a:contourClr>
+                    </a:sp3d>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="3"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="25400">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst>
+                      <a:outerShdw blurRad="228600" dist="127000" dir="2700000" sx="91000" sy="91000" algn="tl" rotWithShape="0">
+                        <a:prstClr val="black">
+                          <a:alpha val="40000"/>
+                        </a:prstClr>
+                      </a:outerShdw>
+                    </a:effectLst>
+                    <a:scene3d>
+                      <a:camera prst="orthographicFront"/>
+                      <a:lightRig rig="threePt" dir="t"/>
+                    </a:scene3d>
+                    <a:sp3d contourW="25400" prstMaterial="metal">
+                      <a:bevelT prst="relaxedInset"/>
+                      <a:contourClr>
+                        <a:schemeClr val="lt1"/>
+                      </a:contourClr>
+                    </a:sp3d>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="4"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln w="25400">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst>
+                      <a:outerShdw blurRad="228600" dist="127000" dir="2700000" sx="91000" sy="91000" algn="tl" rotWithShape="0">
+                        <a:prstClr val="black">
+                          <a:alpha val="40000"/>
+                        </a:prstClr>
+                      </a:outerShdw>
+                    </a:effectLst>
+                    <a:scene3d>
+                      <a:camera prst="orthographicFront"/>
+                      <a:lightRig rig="threePt" dir="t"/>
+                    </a:scene3d>
+                    <a:sp3d contourW="25400" prstMaterial="metal">
+                      <a:bevelT prst="relaxedInset"/>
+                      <a:contourClr>
+                        <a:schemeClr val="lt1"/>
+                      </a:contourClr>
+                    </a:sp3d>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="5"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:ln w="25400">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst>
+                      <a:outerShdw blurRad="228600" dist="127000" dir="2700000" sx="91000" sy="91000" algn="tl" rotWithShape="0">
+                        <a:prstClr val="black">
+                          <a:alpha val="40000"/>
+                        </a:prstClr>
+                      </a:outerShdw>
+                    </a:effectLst>
+                    <a:scene3d>
+                      <a:camera prst="orthographicFront"/>
+                      <a:lightRig rig="threePt" dir="t"/>
+                    </a:scene3d>
+                    <a:sp3d contourW="25400" prstMaterial="metal">
+                      <a:bevelT prst="relaxedInset"/>
+                      <a:contourClr>
+                        <a:schemeClr val="lt1"/>
+                      </a:contourClr>
+                    </a:sp3d>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="6"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="25400">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst>
+                      <a:outerShdw blurRad="228600" dist="127000" dir="2700000" sx="91000" sy="91000" algn="tl" rotWithShape="0">
+                        <a:prstClr val="black">
+                          <a:alpha val="40000"/>
+                        </a:prstClr>
+                      </a:outerShdw>
+                    </a:effectLst>
+                    <a:scene3d>
+                      <a:camera prst="orthographicFront"/>
+                      <a:lightRig rig="threePt" dir="t"/>
+                    </a:scene3d>
+                    <a:sp3d contourW="25400" prstMaterial="metal">
+                      <a:bevelT prst="relaxedInset"/>
+                      <a:contourClr>
+                        <a:schemeClr val="lt1"/>
+                      </a:contourClr>
+                    </a:sp3d>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="7"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="25400">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst>
+                      <a:outerShdw blurRad="228600" dist="127000" dir="2700000" sx="91000" sy="91000" algn="tl" rotWithShape="0">
+                        <a:prstClr val="black">
+                          <a:alpha val="40000"/>
+                        </a:prstClr>
+                      </a:outerShdw>
+                    </a:effectLst>
+                    <a:scene3d>
+                      <a:camera prst="orthographicFront"/>
+                      <a:lightRig rig="threePt" dir="t"/>
+                    </a:scene3d>
+                    <a:sp3d contourW="25400" prstMaterial="metal">
+                      <a:bevelT prst="relaxedInset"/>
+                      <a:contourClr>
+                        <a:schemeClr val="lt1"/>
+                      </a:contourClr>
+                    </a:sp3d>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="8"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="25400">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst>
+                      <a:outerShdw blurRad="228600" dist="127000" dir="2700000" sx="91000" sy="91000" algn="tl" rotWithShape="0">
+                        <a:prstClr val="black">
+                          <a:alpha val="40000"/>
+                        </a:prstClr>
+                      </a:outerShdw>
+                    </a:effectLst>
+                    <a:scene3d>
+                      <a:camera prst="orthographicFront"/>
+                      <a:lightRig rig="threePt" dir="t"/>
+                    </a:scene3d>
+                    <a:sp3d contourW="25400" prstMaterial="metal">
+                      <a:bevelT prst="relaxedInset"/>
+                      <a:contourClr>
+                        <a:schemeClr val="lt1"/>
+                      </a:contourClr>
+                    </a:sp3d>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="9"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="25400">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst>
+                      <a:outerShdw blurRad="228600" dist="127000" dir="2700000" sx="91000" sy="91000" algn="tl" rotWithShape="0">
+                        <a:prstClr val="black">
+                          <a:alpha val="40000"/>
+                        </a:prstClr>
+                      </a:outerShdw>
+                    </a:effectLst>
+                    <a:scene3d>
+                      <a:camera prst="orthographicFront"/>
+                      <a:lightRig rig="threePt" dir="t"/>
+                    </a:scene3d>
+                    <a:sp3d contourW="25400" prstMaterial="metal">
+                      <a:bevelT prst="relaxedInset"/>
+                      <a:contourClr>
+                        <a:schemeClr val="lt1"/>
+                      </a:contourClr>
+                    </a:sp3d>
+                  </c:spPr>
+                </c:dPt>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:sysClr val="window" lastClr="FFFFFF"/>
+                    </a:solidFill>
+                    <a:ln>
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:lumMod val="25000"/>
+                          <a:lumOff val="75000"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="dk1">
+                              <a:lumMod val="65000"/>
+                              <a:lumOff val="35000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="0"/>
+                  <c:showCatName val="1"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="1"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                        <a:prstGeom prst="wedgeRectCallout">
+                          <a:avLst/>
+                        </a:prstGeom>
+                        <a:noFill/>
+                        <a:ln>
+                          <a:noFill/>
+                        </a:ln>
+                      </c15:spPr>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Charts!$A$2:$A$11</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="10"/>
+                      <c:pt idx="0">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-9B82-48D1-9FA9-39D353001870}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredPieSeries>
+          </c:ext>
+        </c:extLst>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="262">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A19EC9E6-436C-C8C0-6F8A-3A84F45E7D7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9F9B8A0-D402-506B-9909-96073D81AC08}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1007,7 +3640,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>335993</v>
+        <v>335982</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1573,12 +4206,206 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9929A14E-24C3-4D64-9E58-8D3A7F917943}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="45.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>60</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2">
+        <f>COUNTA(F2:F1048576)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F26" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F31" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F32" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F37" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1685,5 +4512,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>